--- a/Team-Data/2008-09/11-27-2008-09.xlsx
+++ b/Team-Data/2008-09/11-27-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE2" t="n">
         <v>10</v>
@@ -775,7 +842,7 @@
         <v>19</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
         <v>27</v>
@@ -787,7 +854,7 @@
         <v>21</v>
       </c>
       <c r="AT2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU2" t="n">
         <v>17</v>
@@ -796,7 +863,7 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX2" t="n">
         <v>14</v>
@@ -808,10 +875,10 @@
         <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
         <v>14</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -843,85 +910,85 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.867</v>
+        <v>0.875</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J3" t="n">
-        <v>76</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L3" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="M3" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.35</v>
+        <v>0.343</v>
       </c>
       <c r="O3" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="P3" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.761</v>
+        <v>0.751</v>
       </c>
       <c r="R3" t="n">
         <v>10.6</v>
       </c>
       <c r="S3" t="n">
-        <v>33.2</v>
+        <v>32.8</v>
       </c>
       <c r="T3" t="n">
-        <v>43.8</v>
+        <v>43.3</v>
       </c>
       <c r="U3" t="n">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="V3" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="W3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X3" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>99.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -933,10 +1000,10 @@
         <v>2</v>
       </c>
       <c r="AH3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AI3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -945,34 +1012,34 @@
         <v>6</v>
       </c>
       <c r="AL3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN3" t="n">
         <v>17</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>15</v>
       </c>
       <c r="AO3" t="n">
         <v>2</v>
       </c>
       <c r="AP3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AR3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
         <v>7</v>
       </c>
       <c r="AU3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV3" t="n">
         <v>30</v>
@@ -981,10 +1048,10 @@
         <v>8</v>
       </c>
       <c r="AX3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ3" t="n">
         <v>28</v>
@@ -993,7 +1060,7 @@
         <v>3</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC3" t="n">
         <v>3</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>-4.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE4" t="n">
         <v>25</v>
       </c>
       <c r="AF4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
         <v>25</v>
@@ -1127,7 +1194,7 @@
         <v>26</v>
       </c>
       <c r="AL4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM4" t="n">
         <v>25</v>
@@ -1136,13 +1203,13 @@
         <v>22</v>
       </c>
       <c r="AO4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP4" t="n">
         <v>16</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR4" t="n">
         <v>17</v>
@@ -1166,13 +1233,13 @@
         <v>21</v>
       </c>
       <c r="AY4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ4" t="n">
         <v>19</v>
       </c>
       <c r="BA4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -1207,121 +1274,121 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
         <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4</v>
+        <v>0.438</v>
       </c>
       <c r="H5" t="n">
         <v>48</v>
       </c>
       <c r="I5" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J5" t="n">
-        <v>85.3</v>
+        <v>84.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.425</v>
+        <v>0.43</v>
       </c>
       <c r="L5" t="n">
         <v>5.5</v>
       </c>
       <c r="M5" t="n">
-        <v>15.9</v>
+        <v>15.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.349</v>
+        <v>0.352</v>
       </c>
       <c r="O5" t="n">
-        <v>19.1</v>
+        <v>19.9</v>
       </c>
       <c r="P5" t="n">
-        <v>23.5</v>
+        <v>24.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.806</v>
       </c>
       <c r="R5" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S5" t="n">
-        <v>30.3</v>
+        <v>30</v>
       </c>
       <c r="T5" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U5" t="n">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="V5" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="W5" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.5</v>
+        <v>21.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>97.09999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-4.4</v>
+        <v>-3.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AF5" t="n">
         <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AH5" t="n">
         <v>20</v>
       </c>
       <c r="AI5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM5" t="n">
         <v>22</v>
       </c>
       <c r="AN5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AP5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
         <v>3</v>
@@ -1330,7 +1397,7 @@
         <v>6</v>
       </c>
       <c r="AS5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1348,19 +1415,19 @@
         <v>17</v>
       </c>
       <c r="AY5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AZ5" t="n">
         <v>27</v>
       </c>
       <c r="BA5" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="BB5" t="n">
         <v>17</v>
       </c>
       <c r="BC5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -1389,91 +1456,91 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
         <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.857</v>
+        <v>0.8</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>38.4</v>
+        <v>37.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.09999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0.491</v>
+        <v>0.487</v>
       </c>
       <c r="L6" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="M6" t="n">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.354</v>
+        <v>0.346</v>
       </c>
       <c r="O6" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="P6" t="n">
-        <v>27.1</v>
+        <v>27.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.776</v>
+        <v>0.772</v>
       </c>
       <c r="R6" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="S6" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T6" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U6" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="V6" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Z6" t="n">
         <v>20.9</v>
       </c>
-      <c r="V6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="X6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>20.5</v>
-      </c>
       <c r="AA6" t="n">
-        <v>21.4</v>
+        <v>21.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>104.8</v>
+        <v>103.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>11.7</v>
+        <v>10.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG6" t="n">
         <v>3</v>
@@ -1482,31 +1549,31 @@
         <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK6" t="n">
         <v>2</v>
       </c>
       <c r="AL6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AM6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AO6" t="n">
         <v>6</v>
       </c>
       <c r="AP6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
         <v>19</v>
@@ -1515,13 +1582,13 @@
         <v>13</v>
       </c>
       <c r="AT6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AV6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW6" t="n">
         <v>17</v>
@@ -1533,13 +1600,13 @@
         <v>2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BC6" t="n">
         <v>2</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>1.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE7" t="n">
         <v>14</v>
@@ -1667,7 +1734,7 @@
         <v>11</v>
       </c>
       <c r="AJ7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK7" t="n">
         <v>22</v>
@@ -1676,16 +1743,16 @@
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ7" t="n">
         <v>5</v>
@@ -1709,7 +1776,7 @@
         <v>15</v>
       </c>
       <c r="AX7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY7" t="n">
         <v>9</v>
@@ -1721,7 +1788,7 @@
         <v>25</v>
       </c>
       <c r="BB7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -1753,58 +1820,58 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="H8" t="n">
         <v>48.3</v>
       </c>
       <c r="I8" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="J8" t="n">
-        <v>77.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.452</v>
+        <v>0.448</v>
       </c>
       <c r="L8" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="M8" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="N8" t="n">
-        <v>0.315</v>
+        <v>0.308</v>
       </c>
       <c r="O8" t="n">
-        <v>24.9</v>
+        <v>25.4</v>
       </c>
       <c r="P8" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.779</v>
+        <v>0.778</v>
       </c>
       <c r="R8" t="n">
         <v>10.1</v>
       </c>
       <c r="S8" t="n">
-        <v>31.1</v>
+        <v>31.5</v>
       </c>
       <c r="T8" t="n">
-        <v>41.2</v>
+        <v>41.6</v>
       </c>
       <c r="U8" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V8" t="n">
         <v>16.3</v>
@@ -1816,52 +1883,52 @@
         <v>5.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AA8" t="n">
-        <v>25.5</v>
+        <v>25.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
         <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AH8" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AI8" t="n">
         <v>25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM8" t="n">
         <v>19</v>
       </c>
       <c r="AN8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,19 +1937,19 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR8" t="n">
         <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV8" t="n">
         <v>26</v>
@@ -1891,10 +1958,10 @@
         <v>2</v>
       </c>
       <c r="AX8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AZ8" t="n">
         <v>25</v>
@@ -1906,7 +1973,7 @@
         <v>7</v>
       </c>
       <c r="BC8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>0.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE9" t="n">
         <v>10</v>
@@ -2028,10 +2095,10 @@
         <v>20</v>
       </c>
       <c r="AI9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>16</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>15</v>
       </c>
       <c r="AK9" t="n">
         <v>14</v>
@@ -2052,13 +2119,13 @@
         <v>11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR9" t="n">
         <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT9" t="n">
         <v>13</v>
@@ -2067,13 +2134,13 @@
         <v>10</v>
       </c>
       <c r="AV9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW9" t="n">
         <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY9" t="n">
         <v>11</v>
@@ -2082,7 +2149,7 @@
         <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB9" t="n">
         <v>20</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2262,13 @@
         <v>-3.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
       </c>
       <c r="AF10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG10" t="n">
         <v>23</v>
@@ -2210,19 +2277,19 @@
         <v>6</v>
       </c>
       <c r="AI10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ10" t="n">
         <v>3</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN10" t="n">
         <v>28</v>
@@ -2231,13 +2298,13 @@
         <v>4</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ10" t="n">
         <v>29</v>
       </c>
       <c r="AR10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS10" t="n">
         <v>22</v>
@@ -2267,7 +2334,7 @@
         <v>2</v>
       </c>
       <c r="BB10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>3.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
         <v>6</v>
@@ -2386,7 +2453,7 @@
         <v>10</v>
       </c>
       <c r="AG11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH11" t="n">
         <v>16</v>
@@ -2398,22 +2465,22 @@
         <v>18</v>
       </c>
       <c r="AK11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
         <v>13</v>
       </c>
       <c r="AM11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ11" t="n">
         <v>2</v>
@@ -2422,7 +2489,7 @@
         <v>18</v>
       </c>
       <c r="AS11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT11" t="n">
         <v>6</v>
@@ -2431,7 +2498,7 @@
         <v>26</v>
       </c>
       <c r="AV11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW11" t="n">
         <v>23</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>1.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF12" t="n">
         <v>17</v>
@@ -2580,13 +2647,13 @@
         <v>8</v>
       </c>
       <c r="AK12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN12" t="n">
         <v>12</v>
@@ -2598,7 +2665,7 @@
         <v>28</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR12" t="n">
         <v>15</v>
@@ -2631,7 +2698,7 @@
         <v>15</v>
       </c>
       <c r="BB12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BC12" t="n">
         <v>13</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2765,10 +2832,10 @@
         <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN13" t="n">
         <v>29</v>
@@ -2804,7 +2871,7 @@
         <v>4</v>
       </c>
       <c r="AY13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ13" t="n">
         <v>22</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -2845,88 +2912,88 @@
         </is>
       </c>
       <c r="D14" t="n">
+        <v>13</v>
+      </c>
+      <c r="E14" t="n">
         <v>12</v>
-      </c>
-      <c r="E14" t="n">
-        <v>11</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.917</v>
+        <v>0.923</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>40.1</v>
+        <v>39.8</v>
       </c>
       <c r="J14" t="n">
-        <v>87.09999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="K14" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L14" t="n">
         <v>6.8</v>
       </c>
       <c r="M14" t="n">
-        <v>18</v>
+        <v>17.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.38</v>
+        <v>0.394</v>
       </c>
       <c r="O14" t="n">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="P14" t="n">
-        <v>28.2</v>
+        <v>27.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.743</v>
+        <v>0.747</v>
       </c>
       <c r="R14" t="n">
-        <v>13.8</v>
+        <v>13.4</v>
       </c>
       <c r="S14" t="n">
-        <v>33.2</v>
+        <v>33.7</v>
       </c>
       <c r="T14" t="n">
-        <v>46.9</v>
+        <v>47.1</v>
       </c>
       <c r="U14" t="n">
-        <v>22.7</v>
+        <v>22.4</v>
       </c>
       <c r="V14" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="W14" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="X14" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.9</v>
+        <v>107</v>
       </c>
       <c r="AC14" t="n">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>1</v>
@@ -2947,37 +3014,37 @@
         <v>8</v>
       </c>
       <c r="AL14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AN14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AO14" t="n">
         <v>8</v>
       </c>
       <c r="AP14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT14" t="n">
         <v>2</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2986,13 +3053,13 @@
         <v>6</v>
       </c>
       <c r="AY14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -3105,13 +3172,13 @@
         <v>-6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
       </c>
       <c r="AF15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
         <v>26</v>
@@ -3123,7 +3190,7 @@
         <v>27</v>
       </c>
       <c r="AJ15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK15" t="n">
         <v>21</v>
@@ -3135,25 +3202,25 @@
         <v>26</v>
       </c>
       <c r="AN15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP15" t="n">
         <v>10</v>
       </c>
       <c r="AQ15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS15" t="n">
         <v>15</v>
       </c>
       <c r="AT15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU15" t="n">
         <v>30</v>
@@ -3162,7 +3229,7 @@
         <v>23</v>
       </c>
       <c r="AW15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX15" t="n">
         <v>24</v>
@@ -3174,13 +3241,13 @@
         <v>21</v>
       </c>
       <c r="BA15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB15" t="n">
         <v>27</v>
       </c>
       <c r="BC15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3311,31 +3378,31 @@
         <v>15</v>
       </c>
       <c r="AL16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN16" t="n">
         <v>19</v>
       </c>
       <c r="AO16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ16" t="n">
         <v>26</v>
       </c>
       <c r="AR16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS16" t="n">
         <v>28</v>
       </c>
       <c r="AT16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU16" t="n">
         <v>22</v>
@@ -3347,13 +3414,13 @@
         <v>4</v>
       </c>
       <c r="AX16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY16" t="n">
         <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA16" t="n">
         <v>23</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -3391,28 +3458,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
         <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>0.438</v>
+        <v>0.412</v>
       </c>
       <c r="H17" t="n">
         <v>48.9</v>
       </c>
       <c r="I17" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="J17" t="n">
-        <v>82.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.431</v>
+        <v>0.433</v>
       </c>
       <c r="L17" t="n">
         <v>4.9</v>
@@ -3421,13 +3488,13 @@
         <v>14</v>
       </c>
       <c r="N17" t="n">
-        <v>0.348</v>
+        <v>0.353</v>
       </c>
       <c r="O17" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="P17" t="n">
-        <v>26.2</v>
+        <v>25.8</v>
       </c>
       <c r="Q17" t="n">
         <v>0.754</v>
@@ -3436,19 +3503,19 @@
         <v>13.4</v>
       </c>
       <c r="S17" t="n">
-        <v>31.6</v>
+        <v>30.8</v>
       </c>
       <c r="T17" t="n">
-        <v>44.9</v>
+        <v>44.2</v>
       </c>
       <c r="U17" t="n">
         <v>20.4</v>
       </c>
       <c r="V17" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W17" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X17" t="n">
         <v>3.4</v>
@@ -3457,34 +3524,34 @@
         <v>5.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>25.9</v>
+        <v>26.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>24.3</v>
+        <v>23.9</v>
       </c>
       <c r="AB17" t="n">
         <v>95.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.6</v>
+        <v>-1.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>14</v>
       </c>
       <c r="AF17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH17" t="n">
         <v>2</v>
       </c>
       <c r="AI17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ17" t="n">
         <v>12</v>
@@ -3493,28 +3560,28 @@
         <v>25</v>
       </c>
       <c r="AL17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM17" t="n">
         <v>27</v>
       </c>
       <c r="AN17" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AO17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP17" t="n">
         <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR17" t="n">
         <v>5</v>
       </c>
       <c r="AS17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AT17" t="n">
         <v>5</v>
@@ -3523,19 +3590,19 @@
         <v>14</v>
       </c>
       <c r="AV17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AW17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX17" t="n">
         <v>28</v>
       </c>
       <c r="AY17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA17" t="n">
         <v>4</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3718,13 @@
         <v>-2.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE18" t="n">
         <v>27</v>
       </c>
       <c r="AF18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG18" t="n">
         <v>27</v>
@@ -3675,19 +3742,19 @@
         <v>24</v>
       </c>
       <c r="AL18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM18" t="n">
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP18" t="n">
         <v>22</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>23</v>
       </c>
       <c r="AQ18" t="n">
         <v>6</v>
@@ -3699,7 +3766,7 @@
         <v>20</v>
       </c>
       <c r="AT18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU18" t="n">
         <v>2</v>
@@ -3720,7 +3787,7 @@
         <v>26</v>
       </c>
       <c r="BA18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB18" t="n">
         <v>19</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
         <v>14</v>
@@ -3848,7 +3915,7 @@
         <v>3</v>
       </c>
       <c r="AI19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ19" t="n">
         <v>13</v>
@@ -3857,7 +3924,7 @@
         <v>19</v>
       </c>
       <c r="AL19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM19" t="n">
         <v>9</v>
@@ -3872,34 +3939,34 @@
         <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS19" t="n">
         <v>19</v>
       </c>
       <c r="AT19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW19" t="n">
         <v>25</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY19" t="n">
         <v>17</v>
       </c>
       <c r="AZ19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA19" t="n">
         <v>9</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -3937,100 +4004,100 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
         <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>0.643</v>
+        <v>0.615</v>
       </c>
       <c r="H20" t="n">
         <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>35.6</v>
+        <v>35.8</v>
       </c>
       <c r="J20" t="n">
-        <v>76.3</v>
+        <v>76.5</v>
       </c>
       <c r="K20" t="n">
-        <v>0.466</v>
+        <v>0.467</v>
       </c>
       <c r="L20" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0.393</v>
+        <v>0.381</v>
       </c>
       <c r="O20" t="n">
-        <v>18.4</v>
+        <v>17.8</v>
       </c>
       <c r="P20" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.797</v>
       </c>
       <c r="R20" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>28.6</v>
+        <v>29</v>
       </c>
       <c r="T20" t="n">
-        <v>38.1</v>
+        <v>38.3</v>
       </c>
       <c r="U20" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V20" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="W20" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X20" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z20" t="n">
         <v>20.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>96.90000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="AC20" t="n">
         <v>4.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AE20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF20" t="n">
         <v>5</v>
       </c>
       <c r="AG20" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
         <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AJ20" t="n">
         <v>27</v>
@@ -4039,19 +4106,19 @@
         <v>5</v>
       </c>
       <c r="AL20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AM20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AQ20" t="n">
         <v>4</v>
@@ -4060,19 +4127,19 @@
         <v>26</v>
       </c>
       <c r="AS20" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AT20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AV20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AW20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX20" t="n">
         <v>26</v>
@@ -4084,13 +4151,13 @@
         <v>12</v>
       </c>
       <c r="BA20" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="BB20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BC20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-3.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
         <v>14</v>
@@ -4212,7 +4279,7 @@
         <v>11</v>
       </c>
       <c r="AI21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ21" t="n">
         <v>1</v>
@@ -4239,7 +4306,7 @@
         <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS21" t="n">
         <v>8</v>
@@ -4254,7 +4321,7 @@
         <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4269,10 +4336,10 @@
         <v>30</v>
       </c>
       <c r="BB21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-13</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>30</v>
@@ -4415,7 +4482,7 @@
         <v>20</v>
       </c>
       <c r="AP22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ22" t="n">
         <v>16</v>
@@ -4442,7 +4509,7 @@
         <v>23</v>
       </c>
       <c r="AY22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ22" t="n">
         <v>17</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -4483,88 +4550,88 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F23" t="n">
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>0.75</v>
+        <v>0.733</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="J23" t="n">
-        <v>78.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>24.8</v>
+        <v>25.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0.33</v>
+        <v>0.331</v>
       </c>
       <c r="O23" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="P23" t="n">
         <v>29.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.724</v>
+        <v>0.721</v>
       </c>
       <c r="R23" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="S23" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="T23" t="n">
-        <v>43.4</v>
+        <v>43.1</v>
       </c>
       <c r="U23" t="n">
-        <v>17.4</v>
+        <v>16.9</v>
       </c>
       <c r="V23" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="W23" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="X23" t="n">
         <v>7.2</v>
-      </c>
-      <c r="X23" t="n">
-        <v>7.1</v>
       </c>
       <c r="Y23" t="n">
         <v>4.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>99.8</v>
+        <v>99.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF23" t="n">
         <v>4</v>
@@ -4573,16 +4640,16 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AI23" t="n">
         <v>25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL23" t="n">
         <v>4</v>
@@ -4597,16 +4664,16 @@
         <v>5</v>
       </c>
       <c r="AP23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT23" t="n">
         <v>8</v>
@@ -4615,19 +4682,19 @@
         <v>28</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW23" t="n">
         <v>19</v>
       </c>
       <c r="AX23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ23" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BA23" t="n">
         <v>5</v>
@@ -4636,7 +4703,7 @@
         <v>9</v>
       </c>
       <c r="BC23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>1.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
         <v>14</v>
@@ -4761,7 +4828,7 @@
         <v>9</v>
       </c>
       <c r="AJ24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK24" t="n">
         <v>20</v>
@@ -4779,10 +4846,10 @@
         <v>28</v>
       </c>
       <c r="AP24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>25</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>24</v>
       </c>
       <c r="AR24" t="n">
         <v>1</v>
@@ -4797,10 +4864,10 @@
         <v>19</v>
       </c>
       <c r="AV24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX24" t="n">
         <v>7</v>
@@ -4818,7 +4885,7 @@
         <v>24</v>
       </c>
       <c r="BC24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>4</v>
@@ -4955,7 +5022,7 @@
         <v>17</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
         <v>9</v>
@@ -4964,13 +5031,13 @@
         <v>7</v>
       </c>
       <c r="AQ25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR25" t="n">
         <v>30</v>
       </c>
       <c r="AS25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT25" t="n">
         <v>24</v>
@@ -4982,16 +5049,16 @@
         <v>29</v>
       </c>
       <c r="AW25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX25" t="n">
         <v>16</v>
       </c>
       <c r="AY25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>7</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>6</v>
       </c>
       <c r="BA25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -5029,124 +5096,124 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E26" t="n">
         <v>10</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>0.667</v>
+        <v>0.625</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.6</v>
+        <v>36.1</v>
       </c>
       <c r="J26" t="n">
-        <v>79.7</v>
+        <v>80</v>
       </c>
       <c r="K26" t="n">
-        <v>0.459</v>
+        <v>0.452</v>
       </c>
       <c r="L26" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.419</v>
+        <v>0.418</v>
       </c>
       <c r="O26" t="n">
-        <v>17.9</v>
+        <v>17.3</v>
       </c>
       <c r="P26" t="n">
-        <v>23.2</v>
+        <v>22.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.773</v>
+        <v>0.765</v>
       </c>
       <c r="R26" t="n">
         <v>13.4</v>
       </c>
       <c r="S26" t="n">
-        <v>27.4</v>
+        <v>27.6</v>
       </c>
       <c r="T26" t="n">
-        <v>40.8</v>
+        <v>41</v>
       </c>
       <c r="U26" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V26" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W26" t="n">
         <v>7.7</v>
       </c>
       <c r="X26" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD26" t="n">
         <v>3</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>9</v>
       </c>
       <c r="AE26" t="n">
         <v>6</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AG26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AH26" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AI26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL26" t="n">
         <v>3</v>
       </c>
       <c r="AM26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN26" t="n">
         <v>2</v>
       </c>
       <c r="AO26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP26" t="n">
         <v>23</v>
       </c>
-      <c r="AP26" t="n">
-        <v>22</v>
-      </c>
       <c r="AQ26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR26" t="n">
         <v>4</v>
@@ -5155,34 +5222,34 @@
         <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AU26" t="n">
         <v>8</v>
       </c>
       <c r="AV26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW26" t="n">
         <v>13</v>
       </c>
       <c r="AX26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY26" t="n">
         <v>1</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA26" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB26" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5371,7 @@
         <v>7</v>
       </c>
       <c r="AI27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ27" t="n">
         <v>17</v>
@@ -5322,10 +5389,10 @@
         <v>23</v>
       </c>
       <c r="AO27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ27" t="n">
         <v>9</v>
@@ -5352,16 +5419,16 @@
         <v>25</v>
       </c>
       <c r="AY27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ27" t="n">
         <v>24</v>
       </c>
       <c r="BA27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC27" t="n">
         <v>26</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -5471,10 +5538,10 @@
         <v>1.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF28" t="n">
         <v>10</v>
@@ -5486,19 +5553,19 @@
         <v>3</v>
       </c>
       <c r="AI28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ28" t="n">
         <v>25</v>
       </c>
       <c r="AK28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL28" t="n">
         <v>5</v>
       </c>
       <c r="AM28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN28" t="n">
         <v>4</v>
@@ -5516,7 +5583,7 @@
         <v>29</v>
       </c>
       <c r="AS28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT28" t="n">
         <v>25</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
@@ -5668,7 +5735,7 @@
         <v>3</v>
       </c>
       <c r="AI29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ29" t="n">
         <v>26</v>
@@ -5680,13 +5747,13 @@
         <v>12</v>
       </c>
       <c r="AM29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN29" t="n">
         <v>3</v>
       </c>
       <c r="AO29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
@@ -5707,7 +5774,7 @@
         <v>4</v>
       </c>
       <c r="AV29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW29" t="n">
         <v>29</v>
@@ -5722,7 +5789,7 @@
         <v>1</v>
       </c>
       <c r="BA29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB29" t="n">
         <v>16</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>3.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
         <v>6</v>
@@ -5844,16 +5911,16 @@
         <v>10</v>
       </c>
       <c r="AG30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH30" t="n">
         <v>20</v>
       </c>
       <c r="AI30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK30" t="n">
         <v>3</v>
@@ -5868,13 +5935,13 @@
         <v>18</v>
       </c>
       <c r="AO30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR30" t="n">
         <v>8</v>
@@ -5883,7 +5950,7 @@
         <v>25</v>
       </c>
       <c r="AT30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
@@ -5904,10 +5971,10 @@
         <v>20</v>
       </c>
       <c r="BA30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC30" t="n">
         <v>7</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
@@ -5939,91 +6006,91 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G31" t="n">
-        <v>0.154</v>
+        <v>0.167</v>
       </c>
       <c r="H31" t="n">
         <v>48.4</v>
       </c>
       <c r="I31" t="n">
-        <v>36.5</v>
+        <v>36.7</v>
       </c>
       <c r="J31" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L31" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="M31" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0.282</v>
+        <v>0.291</v>
       </c>
       <c r="O31" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="P31" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.749</v>
+        <v>0.748</v>
       </c>
       <c r="R31" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S31" t="n">
-        <v>29.1</v>
+        <v>28.6</v>
       </c>
       <c r="T31" t="n">
-        <v>40.7</v>
+        <v>40.3</v>
       </c>
       <c r="U31" t="n">
-        <v>19.2</v>
+        <v>18.9</v>
       </c>
       <c r="V31" t="n">
         <v>13.5</v>
       </c>
       <c r="W31" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y31" t="n">
         <v>5.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="AA31" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>96.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-6.8</v>
+        <v>-6.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
       </c>
       <c r="AF31" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AG31" t="n">
         <v>28</v>
@@ -6032,7 +6099,7 @@
         <v>8</v>
       </c>
       <c r="AI31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ31" t="n">
         <v>11</v>
@@ -6041,7 +6108,7 @@
         <v>18</v>
       </c>
       <c r="AL31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM31" t="n">
         <v>18</v>
@@ -6050,31 +6117,31 @@
         <v>30</v>
       </c>
       <c r="AO31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AQ31" t="n">
         <v>21</v>
       </c>
       <c r="AR31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS31" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AT31" t="n">
         <v>22</v>
       </c>
       <c r="AU31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX31" t="n">
         <v>20</v>
@@ -6083,16 +6150,16 @@
         <v>20</v>
       </c>
       <c r="AZ31" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB31" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BC31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-27-2008-09</t>
+          <t>2008-11-27</t>
         </is>
       </c>
     </row>
